--- a/Project/testdata/data.xlsx
+++ b/Project/testdata/data.xlsx
@@ -743,7 +743,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>basket</v>
+        <v>Basket</v>
       </c>
       <c r="B4" t="str">
         <v>creativity</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Continue shopping</v>
+        <v>Continue Shopping</v>
       </c>
     </row>
   </sheetData>

--- a/Project/testdata/data.xlsx
+++ b/Project/testdata/data.xlsx
@@ -727,7 +727,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Search</v>
+        <v>Search by brand</v>
       </c>
       <c r="B2" t="str">
         <v>bikes</v>
@@ -743,7 +743,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>basket</v>
+        <v>Add to Basket</v>
       </c>
       <c r="B4" t="str">
         <v>creativity</v>

--- a/Project/testdata/data.xlsx
+++ b/Project/testdata/data.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ltimindtree-my.sharepoint.com/personal/parth_10853367_ltimindtree_com/Documents/Desktop/Testing Project/Hybrid/1bc7b2d9-96c7-46e0-81e2-735174028d25-b19e1e76-4464-4c0d-8112-3efd3a071fc4/Project/testdata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_32DD5461245B4C54916908D0DF167EB883CFB542" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D68E8A11-F0DC-43FC-AB40-F0B76ABBE3BC}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="ashutoshExcel" sheetId="1" r:id="rId1"/>
     <sheet name="sasiExcel" sheetId="2" r:id="rId2"/>
@@ -10,37 +20,205 @@
     <sheet name="karunaexcel" sheetId="5" r:id="rId5"/>
     <sheet name="saptarshiexcel" sheetId="6" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+  <si>
+    <t>KEYWORDS</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>SEARCH BAR DATA</t>
+  </si>
+  <si>
+    <t>Early</t>
+  </si>
+  <si>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>https://theentertainer.zendesk.com/hc/en-gb/articles/6495305266833-Contact-Us</t>
+  </si>
+  <si>
+    <t>Contact Us – The Entertainer</t>
+  </si>
+  <si>
+    <t>About us</t>
+  </si>
+  <si>
+    <t>https://theentertainer.zendesk.com/hc/en-gb/articles/6480509734289-Delivery-options</t>
+  </si>
+  <si>
+    <t>Delivery options – The Entertainer</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/product-safety-notices</t>
+  </si>
+  <si>
+    <t>_x000D_
+ Product Safety Notices | Early Learning Centre</t>
+  </si>
+  <si>
+    <t>https://theentertainer.zendesk.com/hc/en-gb/articles/4402417396241-Returns</t>
+  </si>
+  <si>
+    <t>Returns – The Entertainer</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Login | Early Learning Centre</t>
+  </si>
+  <si>
+    <t>https://theentertainer.zendesk.com/hc/en-gb</t>
+  </si>
+  <si>
+    <t>The Entertainer</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/privacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Privacy | Early Learning Centre</t>
+  </si>
+  <si>
+    <t>https://theentertainer.zendesk.com/hc/en-gb/articles/32765165894801-How-to-complain</t>
+  </si>
+  <si>
+    <t>How to complain – The Entertainer</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/aboutus</t>
+  </si>
+  <si>
+    <t>About us | Early Learning Centre</t>
+  </si>
+  <si>
+    <t>Useful links</t>
+  </si>
+  <si>
+    <t>https://www.thetoyshop.com/store-finder</t>
+  </si>
+  <si>
+    <t>Find A Store | The Entertainer</t>
+  </si>
+  <si>
+    <t>https://www.thetoyshop.com/weee</t>
+  </si>
+  <si>
+    <t>WEEE, Batteries and Packaging</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/press</t>
+  </si>
+  <si>
+    <t>Press Office | Early Learning Centre</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/affiliates</t>
+  </si>
+  <si>
+    <t>Affiliates | Early Learning Centre</t>
+  </si>
+  <si>
+    <t>https://careers.thetoyshop.com/</t>
+  </si>
+  <si>
+    <t>Careers - The Entertainer</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/gift-cards/The-Entertainer-%26-Early-Learning-Centre-Gift-Card-%C2%A310/p/99880000001_10</t>
+  </si>
+  <si>
+    <t>The Entertainer &amp; Early Learning Centre Gift Card £10 | Early Learning Centre</t>
+  </si>
+  <si>
+    <t>https://www.elc.co.uk/klarna</t>
+  </si>
+  <si>
+    <t>Buy Now Pay Later For Kids Toys with Klarna | ELC</t>
+  </si>
+  <si>
+    <t>Available</t>
+  </si>
+  <si>
+    <t>paw-patrol</t>
+  </si>
+  <si>
+    <t>Basket</t>
+  </si>
+  <si>
+    <t>Gift</t>
+  </si>
+  <si>
+    <t>Brands</t>
+  </si>
+  <si>
+    <t>Explore</t>
+  </si>
+  <si>
+    <t>Order Total</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>new-born-baby-gift-ideas</t>
+  </si>
+  <si>
+    <t>soft-toys</t>
+  </si>
+  <si>
+    <t>Home Delivery</t>
+  </si>
+  <si>
+    <t>KEYWORDS / TEXT</t>
+  </si>
+  <si>
+    <t>Search by brand</t>
+  </si>
+  <si>
+    <t>bikes</t>
+  </si>
+  <si>
+    <t>minutes</t>
+  </si>
+  <si>
+    <t>cart</t>
+  </si>
+  <si>
+    <t>Add to Basket</t>
+  </si>
+  <si>
+    <t>creativity</t>
+  </si>
+  <si>
+    <t>Check out</t>
+  </si>
+  <si>
+    <t>Continue shopping</t>
+  </si>
+  <si>
+    <t>Puzzles</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>Learning Description</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -70,14 +248,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,367 +591,378 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>KEYWORDS</v>
-      </c>
-      <c r="B1" t="str">
-        <v>URL</v>
-      </c>
-      <c r="C1" t="str">
-        <v>SEARCH BAR DATA</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Learning</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Puzzles</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Puzzles</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Early</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Cars</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Cars</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError sqref="A1:C1 A3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>URL</v>
-      </c>
-      <c r="B1" t="str">
-        <v>TITLE</v>
-      </c>
-      <c r="C1" t="str">
-        <v>KEYWORDS</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>https://theentertainer.zendesk.com/hc/en-gb/articles/6495305266833-Contact-Us</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Contact Us – The Entertainer</v>
-      </c>
-      <c r="C2" t="str">
-        <v>About us</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>https://theentertainer.zendesk.com/hc/en-gb/articles/6480509734289-Delivery-options</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Delivery options – The Entertainer</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>https://www.elc.co.uk/product-safety-notices</v>
-      </c>
-      <c r="B4" t="str" xml:space="preserve">
-        <v xml:space="preserve">_x000d_
- Product Safety Notices | Early Learning Centre</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>https://theentertainer.zendesk.com/hc/en-gb/articles/4402417396241-Returns</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Returns – The Entertainer</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>https://www.elc.co.uk/login</v>
-      </c>
-      <c r="B6" t="str">
-        <v xml:space="preserve">  Login | Early Learning Centre</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>https://theentertainer.zendesk.com/hc/en-gb</v>
-      </c>
-      <c r="B7" t="str">
-        <v>The Entertainer</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>https://www.elc.co.uk/privacy</v>
-      </c>
-      <c r="B8" t="str">
-        <v xml:space="preserve"> Privacy | Early Learning Centre</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>https://theentertainer.zendesk.com/hc/en-gb/articles/32765165894801-How-to-complain</v>
-      </c>
-      <c r="B9" t="str">
-        <v>How to complain – The Entertainer</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+    <ignoredError sqref="A1:C9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>URL</v>
-      </c>
-      <c r="B1" t="str">
-        <v>TITLE</v>
-      </c>
-      <c r="C1" t="str">
-        <v>KEYWORDS</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>https://www.elc.co.uk/aboutus</v>
-      </c>
-      <c r="B2" t="str">
-        <v>About us | Early Learning Centre</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Useful links</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>https://www.thetoyshop.com/store-finder</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Find A Store | The Entertainer</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>https://www.thetoyshop.com/weee</v>
-      </c>
-      <c r="B4" t="str">
-        <v>WEEE, Batteries and Packaging</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>https://www.elc.co.uk/press</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Press Office | Early Learning Centre</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>https://www.elc.co.uk/affiliates</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Affiliates | Early Learning Centre</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>https://careers.thetoyshop.com/</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Careers - The Entertainer</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>https://www.elc.co.uk/gift-cards/The-Entertainer-%26-Early-Learning-Centre-Gift-Card-%C2%A310/p/99880000001_10</v>
-      </c>
-      <c r="B8" t="str">
-        <v>The Entertainer &amp; Early Learning Centre Gift Card £10 | Early Learning Centre</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>https://www.elc.co.uk/klarna</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Buy Now Pay Later For Kids Toys with Klarna | ELC</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+    <ignoredError sqref="A1:C9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>KEYWORDS</v>
-      </c>
-      <c r="B1" t="str">
-        <v>URL</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Available</v>
-      </c>
-      <c r="B2" t="str">
-        <v>paw-patrol</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Basket</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Gift</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Brands</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Explore</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Order Total</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError sqref="A1:B6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>KEYWORDS</v>
-      </c>
-      <c r="B1" t="str">
-        <v>URL</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Home</v>
-      </c>
-      <c r="B2" t="str">
-        <v>new-born-baby-gift-ideas</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Brands</v>
-      </c>
-      <c r="B3" t="str">
-        <v>soft-toys</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Home Delivery</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError sqref="A1:B4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>KEYWORDS / TEXT</v>
-      </c>
-      <c r="B1" t="str">
-        <v>URL</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Search by brand</v>
-      </c>
-      <c r="B2" t="str">
-        <v>bikes</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>minutes</v>
-      </c>
-      <c r="B3" t="str">
-        <v>cart</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Add to Basket</v>
-      </c>
-      <c r="B4" t="str">
-        <v>creativity</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Check out</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Continue shopping</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError sqref="A1:B6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>